--- a/analysis/econometrics_outputs/contdid/Graficos/unemployment/dose/contdid_cosine_nearest_dose_acrt.xlsx
+++ b/analysis/econometrics_outputs/contdid/Graficos/unemployment/dose/contdid_cosine_nearest_dose_acrt.xlsx
@@ -488,10 +488,10 @@
         <v>0.778484368111667</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>1.47502757291166</v>
+        <v>2.38499291787001</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -510,10 +510,10 @@
         <v>0.793393783438106</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>1.42917268084171</v>
+        <v>2.31478353294637</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -532,10 +532,10 @@
         <v>0.802880675004097</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>1.39975423924263</v>
+        <v>2.27149805946788</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -554,10 +554,10 @@
         <v>0.861820263271038</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>1.2121635503919</v>
+        <v>2.02993856733816</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -576,10 +576,10 @@
         <v>0.877604292105276</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>1.16028802072161</v>
+        <v>1.95478886815137</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -598,10 +598,10 @@
         <v>0.898707685310284</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>1.08962870169952</v>
+        <v>1.85239139633183</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -620,10 +620,10 @@
         <v>0.920731783375331</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>1.01407701599293</v>
+        <v>1.74285414068372</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -642,10 +642,10 @@
         <v>0.934154655172498</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>0.966993165730231</v>
+        <v>1.67456252800274</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -664,10 +664,10 @@
         <v>0.934154655172498</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>0.966993165730231</v>
+        <v>1.67456252800274</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -686,10 +686,10 @@
         <v>0.945847473722233</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>0.925253767282623</v>
+        <v>1.61400358252513</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -708,10 +708,10 @@
         <v>0.967558421738299</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>0.845705311728296</v>
+        <v>1.48646593553223</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -730,10 +730,10 @@
         <v>0.973528950860132</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>0.823302227652118</v>
+        <v>1.44855146522797</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -752,10 +752,10 @@
         <v>0.99161631354869</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>0.753810947329328</v>
+        <v>1.32507094475727</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -774,10 +774,10 @@
         <v>1.00130881650105</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>0.715431770738612</v>
+        <v>1.24997389885734</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -796,10 +796,10 @@
         <v>1.0199782001115</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>0.638779845846362</v>
+        <v>1.15102609609854</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -818,10 +818,10 @@
         <v>1.02420404006374</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>0.620849585445751</v>
+        <v>1.12334345332826</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -840,10 +840,10 @@
         <v>1.02865953160373</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>0.60167883698683</v>
+        <v>1.09273510402583</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -862,10 +862,10 @@
         <v>1.06574306381222</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>0.427801909828464</v>
+        <v>0.833059293974823</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -884,10 +884,10 @@
         <v>1.08325824574874</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>0.355056954247227</v>
+        <v>0.727370114412192</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -906,10 +906,10 @@
         <v>1.08325824574874</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>0.355056954247227</v>
+        <v>0.727370114412192</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -928,10 +928,10 @@
         <v>1.09229620112638</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>0.332213442722515</v>
+        <v>0.612676046248794</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -950,10 +950,10 @@
         <v>1.10169527592155</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>0.304884461997714</v>
+        <v>0.509600518548342</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -972,10 +972,10 @@
         <v>1.10367509099239</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>0.298373727248348</v>
+        <v>0.508214586955904</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -994,10 +994,10 @@
         <v>1.11177188843071</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>0.265902029341919</v>
+        <v>0.445787677975668</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1016,10 +1016,10 @@
         <v>1.11417246376737</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>0.252043466168201</v>
+        <v>0.40009913525561</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -1038,10 +1038,10 @@
         <v>1.11528691624834</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>0.243416458820663</v>
+        <v>0.377710953057218</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1060,10 +1060,10 @@
         <v>1.11325186323092</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>0.229646508555516</v>
+        <v>0.34007553549535</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1082,10 +1082,10 @@
         <v>1.10727370340433</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>0.217844247740272</v>
+        <v>0.355853539511434</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1104,10 +1104,10 @@
         <v>1.10447254958666</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>0.197057839537187</v>
+        <v>0.365655761614926</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1126,10 +1126,10 @@
         <v>1.10117073546724</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>0.176053810935823</v>
+        <v>0.369234190174122</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -1148,10 +1148,10 @@
         <v>1.09617647581875</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>0.149134862935733</v>
+        <v>0.363051636093956</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1170,10 +1170,10 @@
         <v>1.08345062897237</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>0.113954811019381</v>
+        <v>0.351634318205702</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -1192,10 +1192,10 @@
         <v>1.04352099388674</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>0.0979088437324962</v>
+        <v>0.37112113017638</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -1214,10 +1214,10 @@
         <v>1.03113741099844</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0.113934491528276</v>
+        <v>0.367893227254054</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -1236,10 +1236,10 @@
         <v>1.01885652529822</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>0.127309317231587</v>
+        <v>0.382213846796558</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -1258,10 +1258,10 @@
         <v>0.998726428317717</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>0.144966396043532</v>
+        <v>0.422838395417319</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1280,10 +1280,10 @@
         <v>0.986224595437874</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>0.153770828110088</v>
+        <v>0.42536454748689</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -1302,10 +1302,10 @@
         <v>0.967030450065681</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>0.164679215856821</v>
+        <v>0.426035012858254</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -1324,10 +1324,10 @@
         <v>0.963799223727669</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>0.16624229419951</v>
+        <v>0.425940004799202</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -1346,10 +1346,10 @@
         <v>0.859555450260054</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>0.187061504291145</v>
+        <v>0.432937995832951</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -1368,10 +1368,10 @@
         <v>0.789364605879961</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>0.179438240317652</v>
+        <v>0.417130982341237</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -1390,10 +1390,10 @@
         <v>0.773794009073024</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>0.176396195926661</v>
+        <v>0.411339526284442</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -1412,10 +1412,10 @@
         <v>0.734974441015695</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>0.176704082973041</v>
+        <v>0.390575736213409</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -1434,10 +1434,10 @@
         <v>0.715132488992095</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>0.178253084012913</v>
+        <v>0.383056017608044</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -1456,10 +1456,10 @@
         <v>0.68289207133985</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>0.180776249940397</v>
+        <v>0.370799007732722</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -1478,10 +1478,10 @@
         <v>0.528650333234166</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>0.192965299275749</v>
+        <v>0.350462258193073</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -1500,10 +1500,10 @@
         <v>0.440255925667476</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>0.2000515298365</v>
+        <v>0.320622428746879</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -1522,10 +1522,10 @@
         <v>0.311318965550559</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>0.21054933742623</v>
+        <v>0.277924158435691</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -1544,10 +1544,10 @@
         <v>0.206480536951554</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>0.219258267880357</v>
+        <v>0.225896161088999</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -1566,10 +1566,10 @@
         <v>0.154447584083079</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>0.223651220493521</v>
+        <v>0.213817096283732</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -1588,10 +1588,10 @@
         <v>0.125901343490693</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>0.226084300997376</v>
+        <v>0.214930945597934</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -1610,10 +1610,10 @@
         <v>0.125901343490693</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>0.226084300997376</v>
+        <v>0.214930945597934</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -1632,10 +1632,10 @@
         <v>0.112087567255283</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>0.227268043461043</v>
+        <v>0.215288643371388</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -1654,10 +1654,10 @@
         <v>0.0810616753677024</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>0.224041998614264</v>
+        <v>0.212017173874255</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -1676,10 +1676,10 @@
         <v>0.0393620919353264</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>0.217601851136002</v>
+        <v>0.218819162425716</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -1698,10 +1698,10 @@
         <v>0.0239493678591282</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>0.215169682984875</v>
+        <v>0.218543040769887</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -1720,10 +1720,10 @@
         <v>-0.0647644462645697</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>0.220663018091198</v>
+        <v>0.198065341618234</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -1742,10 +1742,10 @@
         <v>-0.0927669820876114</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>0.227763517262045</v>
+        <v>0.193073423525006</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -1764,10 +1764,10 @@
         <v>-0.143034756211326</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>0.240378545095794</v>
+        <v>0.191525847941335</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -1786,10 +1786,10 @@
         <v>-0.162564170178292</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>0.245226374206674</v>
+        <v>0.189535070358396</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
@@ -1808,10 +1808,10 @@
         <v>-0.271556679657532</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>0.263050627289114</v>
+        <v>0.228384668525511</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -1830,10 +1830,10 @@
         <v>-0.322581462362844</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>0.268747255161196</v>
+        <v>0.240378996268742</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -1852,10 +1852,10 @@
         <v>-0.340822324406643</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>0.270934050053853</v>
+        <v>0.233524911079391</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -1874,10 +1874,10 @@
         <v>-0.382559752658696</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>0.276483684471535</v>
+        <v>0.233449279365109</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
@@ -1896,10 +1896,10 @@
         <v>-0.398537778858225</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>0.265722831170254</v>
+        <v>0.259582801952444</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -1918,10 +1918,10 @@
         <v>-0.411392700357974</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>0.253164375781724</v>
+        <v>0.28672558794012</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
@@ -1940,10 +1940,10 @@
         <v>-0.418552597874245</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>0.243081817824672</v>
+        <v>0.289004158964294</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
@@ -1962,10 +1962,10 @@
         <v>-0.424186368656295</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>0.230497160393654</v>
+        <v>0.296353895700585</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
@@ -1984,10 +1984,10 @@
         <v>-0.424636680696884</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>0.203771338629751</v>
+        <v>0.287070135744009</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
@@ -2006,10 +2006,10 @@
         <v>-0.419762209299485</v>
       </c>
       <c r="F75" s="1" t="n">
-        <v>0.210256116012345</v>
+        <v>0.298795039604132</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
@@ -2028,10 +2028,10 @@
         <v>-0.417306342047027</v>
       </c>
       <c r="F76" s="1" t="n">
-        <v>0.212553412802269</v>
+        <v>0.299855027526177</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
@@ -2050,10 +2050,10 @@
         <v>-0.414272471531115</v>
       </c>
       <c r="F77" s="1" t="n">
-        <v>0.213422716775478</v>
+        <v>0.299549049371333</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -2072,10 +2072,10 @@
         <v>-0.406602210612666</v>
       </c>
       <c r="F78" s="1" t="n">
-        <v>0.213956551015164</v>
+        <v>0.3016538667334</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
@@ -2094,10 +2094,10 @@
         <v>-0.387892213349261</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>0.213342831397192</v>
+        <v>0.301805280438965</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
@@ -2116,10 +2116,10 @@
         <v>-0.359949094768667</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>0.2102417777949</v>
+        <v>0.291805522131272</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
@@ -2138,10 +2138,10 @@
         <v>-0.302760287471939</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>0.200581748513868</v>
+        <v>0.271336229940448</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
@@ -2160,10 +2160,10 @@
         <v>-0.290561472333152</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>0.201060018924756</v>
+        <v>0.264871146973746</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
@@ -2182,10 +2182,10 @@
         <v>-0.213778479048891</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>0.260247846171609</v>
+        <v>0.246253001578541</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
@@ -2204,10 +2204,10 @@
         <v>-0.132520487027626</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>0.267072289915291</v>
+        <v>0.231122174193433</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
@@ -2226,10 +2226,10 @@
         <v>-0.0906587750489783</v>
       </c>
       <c r="F85" s="1" t="n">
-        <v>0.26975342299278</v>
+        <v>0.231859388760849</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
@@ -2248,10 +2248,10 @@
         <v>0.0159437104231312</v>
       </c>
       <c r="F86" s="1" t="n">
-        <v>0.274799167824736</v>
+        <v>0.206585370990828</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
@@ -2270,10 +2270,10 @@
         <v>0.0225250893226024</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>0.275042591572626</v>
+        <v>0.206479883875481</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
@@ -2292,10 +2292,10 @@
         <v>0.145557034315627</v>
       </c>
       <c r="F88" s="1" t="n">
-        <v>0.278474784876166</v>
+        <v>0.220567492231064</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
@@ -2314,10 +2314,10 @@
         <v>0.287384474071972</v>
       </c>
       <c r="F89" s="1" t="n">
-        <v>0.273650926568783</v>
+        <v>0.233297323450436</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -2336,10 +2336,10 @@
         <v>0.417940227128322</v>
       </c>
       <c r="F90" s="1" t="n">
-        <v>0.268334317388857</v>
+        <v>0.230095133986519</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
@@ -2358,10 +2358,10 @@
         <v>0.499115568391774</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>0.28033861200844</v>
+        <v>0.251459632963321</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
@@ -2380,10 +2380,10 @@
         <v>0.501487533392093</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>0.280322927602884</v>
+        <v>0.251517928265271</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -2402,10 +2402,10 @@
         <v>0.805509160904799</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>0.276172768531552</v>
+        <v>0.345304270361265</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -2424,10 +2424,10 @@
         <v>1.32134431132912</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>0.262156971062483</v>
+        <v>0.481241165839328</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -2446,10 +2446,10 @@
         <v>3.15096490680564</v>
       </c>
       <c r="F95" s="1" t="n">
-        <v>0.177672038480778</v>
+        <v>1.24477338565489</v>
       </c>
       <c r="G95" s="1" t="n">
-        <v>17.0606590290943</v>
+        <v>3.23591858434237</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
